--- a/apps/api/assets/vocabulary/小学/人教版/四年级上.xlsx
+++ b/apps/api/assets/vocabulary/小学/人教版/四年级上.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -615,6 +615,16 @@
           <t>teacher's desk</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 讲台；讲桌；讲台桌</t>
@@ -864,6 +874,16 @@
           <t>maths book</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -876,6 +896,16 @@
           <t>English book</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 英语书；英文书；数学书</t>
@@ -886,6 +916,16 @@
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Chinese book</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1944,6 +1984,16 @@
           <t>help yourself</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 别客气；请自便；随便吃</t>
@@ -2096,6 +2146,16 @@
           <t>baby brother</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 小弟弟；我的弟弟啊；切入正题</t>
@@ -2321,6 +2381,16 @@
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>football player</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
